--- a/Data/EC/NIT-9007237692.xlsx
+++ b/Data/EC/NIT-9007237692.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26DFA9AF-6E31-4153-A885-9713E2B3165E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C207CB36-E701-4760-AC9B-62FAEB3E179C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{049391A4-D7E6-4D49-831B-832C5B8ADF7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C552508F-1630-4D8A-A514-54A72F2668F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="122">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>MANUEL ENRIQUE TOVAR CORREA</t>
+  </si>
+  <si>
+    <t>2607</t>
   </si>
   <si>
     <t>2606</t>
@@ -767,22 +770,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECA8AB99-89E3-F812-5EB2-1CDF8A111BD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9F83E66-EB6D-4464-0D4E-CE43769B6063}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -791,7 +794,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -804,7 +807,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1133,27 +1136,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8347411A-DD5C-49E2-821D-D412DFB1B449}">
-  <dimension ref="B2:J120"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3A30D9-651A-4D10-BE06-9E5BA3088C6B}">
+  <dimension ref="B2:J121"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1162,7 +1165,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1173,7 +1176,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1184,7 +1187,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1195,10 +1198,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1211,8 +1214,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1227,15 +1230,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>3093651</v>
+        <v>3124900</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1243,27 +1246,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F13" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1283,16 +1286,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>115</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1315,7 +1318,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1338,7 +1341,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1364,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1384,7 +1387,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1407,7 +1410,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1430,7 +1433,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1453,7 +1456,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1476,7 +1479,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1499,7 +1502,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1522,7 +1525,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1545,7 +1548,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1568,7 +1571,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1594,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1614,7 +1617,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1637,7 +1640,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1660,7 +1663,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1683,7 +1686,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1706,7 +1709,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1729,7 +1732,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1752,7 +1755,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1775,7 +1778,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1798,7 +1801,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1821,7 +1824,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1844,7 +1847,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1867,7 +1870,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1890,7 +1893,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1913,7 +1916,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1936,7 +1939,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1959,7 +1962,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1982,7 +1985,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2005,7 +2008,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2028,7 +2031,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2051,7 +2054,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2074,7 +2077,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2097,7 +2100,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2120,7 +2123,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2143,7 +2146,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2166,7 +2169,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2189,7 +2192,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2212,7 +2215,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2235,7 +2238,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2258,7 +2261,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2281,7 +2284,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2304,7 +2307,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2327,7 +2330,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2350,7 +2353,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2373,7 +2376,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2399,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2419,7 +2422,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2442,7 +2445,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2465,7 +2468,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2488,7 +2491,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2511,7 +2514,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2534,7 +2537,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2557,7 +2560,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2580,7 +2583,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2603,7 +2606,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2626,7 +2629,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2649,7 +2652,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2672,7 +2675,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2695,7 +2698,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2718,7 +2721,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2741,7 +2744,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2764,7 +2767,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2787,7 +2790,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2810,7 +2813,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2833,7 +2836,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2856,7 +2859,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2879,7 +2882,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2902,7 +2905,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2925,7 +2928,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2948,7 +2951,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2971,7 +2974,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2994,7 +2997,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3017,7 +3020,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3043,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3063,7 +3066,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3086,7 +3089,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3109,7 +3112,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3132,7 +3135,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3155,7 +3158,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3178,7 +3181,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3201,7 +3204,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3224,7 +3227,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3247,7 +3250,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3270,7 +3273,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3293,7 +3296,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3316,7 +3319,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3339,7 +3342,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3362,7 +3365,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3385,7 +3388,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3408,7 +3411,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3431,7 +3434,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3454,7 +3457,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3477,7 +3480,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3500,7 +3503,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3523,7 +3526,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3546,43 +3549,55 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B114" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="22" t="s">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B114" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F114" s="24">
-        <v>31249</v>
-      </c>
-      <c r="G114" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H114" s="25"/>
-      <c r="I114" s="25"/>
-      <c r="J114" s="26"/>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B119" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C119" s="32"/>
-      <c r="H119" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="F114" s="18">
+        <v>31249</v>
+      </c>
+      <c r="G114" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="20"/>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B115" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F115" s="24">
+        <v>31249</v>
+      </c>
+      <c r="G115" s="24">
+        <v>781242</v>
+      </c>
+      <c r="H115" s="25"/>
+      <c r="I115" s="25"/>
+      <c r="J115" s="26"/>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C120" s="32"/>
       <c r="H120" s="1" t="s">
@@ -3591,12 +3606,23 @@
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
     </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B121" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C121" s="32"/>
+      <c r="H121" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B121:C121"/>
     <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="H121:J121"/>
     <mergeCell ref="H120:J120"/>
-    <mergeCell ref="H119:J119"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
